--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12111" windowHeight="19251" tabRatio="798" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
-    <sheet name="1、工单需求-内容录入" sheetId="3" r:id="rId2"/>
+    <sheet name="1、工单需求-元数据录入" sheetId="3" r:id="rId2"/>
     <sheet name="2、功能清单-内容录入" sheetId="1" r:id="rId3"/>
     <sheet name="3、FPA工作量评估-元数据录入" sheetId="4" r:id="rId4"/>
     <sheet name="4、项目需求说明书-元数据录入" sheetId="5" r:id="rId5"/>
@@ -195,7 +195,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B12" authorId="0">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="278">
   <si>
     <t>绿色单元格</t>
   </si>
@@ -339,16 +339,25 @@
     <t>总体描述</t>
   </si>
   <si>
-    <t>#AI生成-工单内容#</t>
+    <t>#AI生成#根据${工单内容}，生成总体描述，要求200~300字</t>
   </si>
   <si>
     <t>建设目标</t>
   </si>
   <si>
+    <t>#AI生成#根据${工单内容}，生成建设目标，要求200~300字</t>
+  </si>
+  <si>
     <t>建设必要性</t>
   </si>
   <si>
+    <t>#AI生成#根据${工单内容}，生成建设必要性，要求200~300字</t>
+  </si>
+  <si>
     <t>系统概况</t>
+  </si>
+  <si>
+    <t>#AI生成#根据${工单内容}，生成系统概况，要求200~300字</t>
   </si>
   <si>
     <t>入口</t>
@@ -960,7 +969,10 @@
     <t>调整因子中的功能概述</t>
   </si>
   <si>
-    <t>#AI生成#基于【三级模块】的内容，概括项目的主要功能模块，说明系统属于业务处理还是管理支撑类型</t>
+    <t>#AI生成#
+根据${三级模块}的全部内容，概括项目的主要功能模块，判定系统属于业务处理还是管理支撑类型。
+按照以下示例的格式输出：
+本项目主要完成功能参与垂直行业配置、行业人员认证、下单页面自定义配置、用户下单、订单查看等模块，属于业务处理。</t>
   </si>
   <si>
     <t>调整因子中的子系统名称</t>
@@ -972,8 +984,15 @@
     <t>调整因子中的可靠性描述</t>
   </si>
   <si>
-    <t>#AI生成#系统功能中涉及与可靠性方面的模块有【三级模块整体功能描述】，请基于这些模块内容，生成一段可靠性需求描述，要求包含：1）结合项目业务场景说明可靠性为何重要；2）数据备份和容灾要求；3）7×24小时不间断运行要求；4）模块更新不相互影响的要求
-请参考以下示例风格：结合业务场景说明可靠性重要性，提出具体的数据备份和容灾措施，明确运行时间和模块独立性要求。</t>
+    <t>#AI生成#
+根据${三级模块整体功能描述}中的全部内容，提取其中涉及与可靠性方面的模块，生成一段可靠性需求描述，
+要求包含：
+1. 结合项目业务场景说明可靠性为何重要；
+2. 数据备份和容灾要求；
+3. 7×24小时不间断运行要求；
+4. 模块更新不相互影响的要求
+请参考以下示例风格：
+结合业务场景说明可靠性重要性，提出具体的数据备份和容灾措施，明确运行时间和模块独立性要求。</t>
   </si>
   <si>
     <t>数量</t>
@@ -997,10 +1016,11 @@
     <t>客户需求</t>
   </si>
   <si>
-    <t>功能用户-发起者</t>
-  </si>
-  <si>
-    <t>操作员</t>
+    <t>功能用户-发起者判定</t>
+  </si>
+  <si>
+    <t>默认：操作员
+分销：分销员</t>
   </si>
   <si>
     <t>功能用户-接收者判定</t>
@@ -1022,6 +1042,9 @@
   </si>
   <si>
     <t>IF(L{row}=\"新增\",1,IF(L{row}=\"复用\",1/3,0))</t>
+  </si>
+  <si>
+    <t>附件3-${工单编号}-${工单名称}（${子系统（模块）}）项目需求清单V1.0.0.docx</t>
   </si>
   <si>
     <t>项目信息概览-标题</t>
@@ -1335,12 +1358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1878,7 +1901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1906,14 +1929,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2528,26 +2554,26 @@
   </cols>
   <sheetData>
     <row r="4" ht="47" customHeight="1" spans="1:2">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" spans="1:2">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2572,12 +2598,12 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA('2、功能清单-内容录入'!A:A)-1</f>
@@ -2586,7 +2612,7 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B3" s="3">
         <f>COUNTA('2、功能清单-内容录入'!B:B)-1</f>
@@ -2595,7 +2621,7 @@
     </row>
     <row r="4" ht="43" customHeight="1" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTA('2、功能清单-内容录入'!C:C)-1</f>
@@ -2604,7 +2630,7 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTA('2、功能清单-内容录入'!D:D)-1</f>
@@ -2613,7 +2639,7 @@
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTA('2、功能清单-内容录入'!G:G)-1</f>
@@ -2637,7 +2663,7 @@
     <col min="2" max="2" width="117.36036036036" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="29" customFormat="1" ht="38" customHeight="1" spans="1:2">
+    <row r="1" s="30" customFormat="1" ht="38" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -2646,59 +2672,59 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="183.45" spans="1:2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:2">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>15</v>
+      <c r="B6" s="32" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:2">
-      <c r="A7" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>15</v>
+      <c r="A7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:2">
-      <c r="A8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>15</v>
+      <c r="A8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2713,1121 +2739,1121 @@
   <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.72972972972973" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="10.1351351351351" style="20" customWidth="1"/>
-    <col min="2" max="2" width="12.6666666666667" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.7297297297297" style="20" customWidth="1"/>
-    <col min="4" max="4" width="19.3333333333333" style="20" customWidth="1"/>
-    <col min="5" max="5" width="23.1621621621622" style="20" customWidth="1"/>
-    <col min="6" max="6" width="44.3333333333333" style="20" customWidth="1"/>
-    <col min="7" max="7" width="35.5225225225225" style="20" customWidth="1"/>
-    <col min="8" max="8" width="23.5315315315315" style="20" customWidth="1"/>
-    <col min="9" max="9" width="55.045045045045" style="20" customWidth="1"/>
-    <col min="10" max="16384" width="8.72972972972973" style="20"/>
+    <col min="1" max="1" width="10.1351351351351" style="21" customWidth="1"/>
+    <col min="2" max="2" width="12.6666666666667" style="21" customWidth="1"/>
+    <col min="3" max="3" width="13.7297297297297" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.3333333333333" style="21" customWidth="1"/>
+    <col min="5" max="5" width="23.1621621621622" style="21" customWidth="1"/>
+    <col min="6" max="6" width="44.3333333333333" style="21" customWidth="1"/>
+    <col min="7" max="7" width="35.5225225225225" style="21" customWidth="1"/>
+    <col min="8" max="8" width="23.5315315315315" style="21" customWidth="1"/>
+    <col min="9" max="9" width="55.045045045045" style="21" customWidth="1"/>
+    <col min="10" max="16384" width="8.72972972972973" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="1" ht="49" customHeight="1" spans="1:9">
-      <c r="A1" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="21" t="s">
+    <row r="1" s="20" customFormat="1" ht="49" customHeight="1" spans="1:9">
+      <c r="A1" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="F1" s="22" t="s">
         <v>27</v>
       </c>
+      <c r="G1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9">
-      <c r="A2" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="C2" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="D2" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="F2" s="24" t="s">
         <v>35</v>
       </c>
+      <c r="G2" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3" ht="28.3" spans="1:9">
-      <c r="A3" s="25"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="23" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" ht="29" customHeight="1" spans="1:9">
+      <c r="A4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:9">
+      <c r="A5" s="26"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="28.3" spans="1:9">
+      <c r="A6" s="26"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" ht="39" customHeight="1" spans="1:9">
+      <c r="A7" s="26"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" ht="14.15" spans="1:9">
+      <c r="A8" s="26"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="47" customHeight="1" spans="1:9">
+      <c r="A9" s="26"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="29" customHeight="1" spans="1:9">
-      <c r="A4" s="25"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="23" t="s">
+      <c r="F9" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="35" customHeight="1" spans="1:9">
+      <c r="A10" s="26"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:9">
+      <c r="A11" s="26"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" ht="14.15" spans="1:9">
+      <c r="A12" s="26"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="28.3" spans="1:9">
+      <c r="A13" s="26"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:9">
-      <c r="A5" s="25"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="23" t="s">
+      <c r="F13" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="99" spans="1:9">
+      <c r="A14" s="26"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" ht="99" spans="1:9">
+      <c r="A15" s="26"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" ht="14.15" spans="1:9">
+      <c r="A16" s="26"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" ht="28.3" spans="1:9">
+      <c r="A17" s="26"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" ht="14.15" spans="1:9">
+      <c r="A18" s="26"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" ht="28.3" spans="1:9">
+      <c r="A19" s="26"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" ht="28.3" spans="1:9">
-      <c r="A6" s="25"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="23" t="s">
+      <c r="F19" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" ht="99" spans="1:9">
+      <c r="A20" s="26"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" ht="99" spans="1:9">
+      <c r="A21" s="26"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" ht="14.15" spans="1:9">
+      <c r="A22" s="26"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" ht="28.3" spans="1:9">
+      <c r="A23" s="26"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" ht="14.15" spans="1:9">
+      <c r="A24" s="26"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" ht="42.45" spans="1:9">
+      <c r="A25" s="26"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" ht="39" customHeight="1" spans="1:9">
-      <c r="A7" s="25"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="23" t="s">
+      <c r="F25" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" ht="42.45" spans="1:9">
+      <c r="A26" s="26"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" ht="42.45" spans="1:9">
+      <c r="A27" s="26"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" ht="56.55" spans="1:9">
+      <c r="A28" s="26"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" ht="14.15" spans="1:9">
-      <c r="A8" s="25"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="23" t="s">
+      <c r="F28" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" ht="56.55" spans="1:9">
+      <c r="A29" s="26"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" ht="28.3" spans="1:9">
+      <c r="A30" s="26"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" ht="28.3" spans="1:9">
+      <c r="A31" s="26"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="47" customHeight="1" spans="1:9">
-      <c r="A9" s="25"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="23" t="s">
+      <c r="F31" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" ht="28.3" spans="1:9">
+      <c r="A32" s="26"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" ht="28.3" spans="1:9">
+      <c r="A33" s="26"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" ht="14.15" spans="1:9">
+      <c r="A34" s="26"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" ht="14.15" spans="1:9">
+      <c r="A35" s="26"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" ht="14.15" spans="1:9">
+      <c r="A36" s="26"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1" spans="1:9">
+      <c r="A37" s="26"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" ht="35" customHeight="1" spans="1:9">
-      <c r="A10" s="25"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="23" t="s">
+      <c r="F37" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G37" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1" spans="1:9">
+      <c r="A38" s="26"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1" spans="1:9">
+      <c r="A39" s="26"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1" spans="1:9">
+      <c r="A40" s="26"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1" spans="1:9">
+      <c r="A41" s="26"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1" spans="1:9">
+      <c r="A42" s="26"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" s="25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1" spans="1:9">
+      <c r="A43" s="26"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:9">
+      <c r="A44" s="26"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" spans="1:9">
+      <c r="A45" s="26"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E45" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:9">
-      <c r="A11" s="25"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" ht="14.15" spans="1:9">
-      <c r="A12" s="25"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="28.3" spans="1:9">
-      <c r="A13" s="25"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" ht="99" spans="1:9">
-      <c r="A14" s="25"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" ht="99" spans="1:9">
-      <c r="A15" s="25"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" ht="14.15" spans="1:9">
-      <c r="A16" s="25"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="28.3" spans="1:9">
-      <c r="A17" s="25"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" ht="14.15" spans="1:9">
-      <c r="A18" s="25"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" ht="28.3" spans="1:9">
-      <c r="A19" s="25"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" ht="99" spans="1:9">
-      <c r="A20" s="25"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" ht="99" spans="1:9">
-      <c r="A21" s="25"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" ht="14.15" spans="1:9">
-      <c r="A22" s="25"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" ht="28.3" spans="1:9">
-      <c r="A23" s="25"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" ht="14.15" spans="1:9">
-      <c r="A24" s="25"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" ht="42.45" spans="1:9">
-      <c r="A25" s="25"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" ht="42.45" spans="1:9">
-      <c r="A26" s="25"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" ht="42.45" spans="1:9">
-      <c r="A27" s="25"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" ht="56.55" spans="1:9">
-      <c r="A28" s="25"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" ht="56.55" spans="1:9">
-      <c r="A29" s="25"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" ht="28.3" spans="1:9">
-      <c r="A30" s="25"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" ht="28.3" spans="1:9">
-      <c r="A31" s="25"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" ht="28.3" spans="1:9">
-      <c r="A32" s="25"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" ht="28.3" spans="1:9">
-      <c r="A33" s="25"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" ht="14.15" spans="1:9">
-      <c r="A34" s="25"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" ht="14.15" spans="1:9">
-      <c r="A35" s="25"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="H35" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" ht="14.15" spans="1:9">
-      <c r="A36" s="25"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1" spans="1:9">
-      <c r="A37" s="25"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1" spans="1:9">
-      <c r="A38" s="25"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1" spans="1:9">
-      <c r="A39" s="25"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1" spans="1:9">
-      <c r="A40" s="25"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1" spans="1:9">
-      <c r="A41" s="25"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:9">
-      <c r="A42" s="25"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1" spans="1:9">
-      <c r="A43" s="25"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="G43" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="H43" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1" spans="1:9">
-      <c r="A44" s="25"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1" spans="1:9">
-      <c r="A45" s="25"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G45" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" s="24" t="s">
-        <v>142</v>
+      <c r="F45" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:9">
-      <c r="A46" s="25"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="H46" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>144</v>
+      <c r="A46" s="26"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1" spans="1:9">
-      <c r="A47" s="25"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="24" t="s">
+      <c r="A47" s="26"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24" t="s">
         <v>148</v>
       </c>
+      <c r="E47" s="26"/>
+      <c r="F47" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:9">
-      <c r="A48" s="26"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="H48" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>150</v>
+      <c r="A48" s="27"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:9">
-      <c r="A49" s="25"/>
-      <c r="B49" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="24" t="s">
+      <c r="A49" s="26"/>
+      <c r="B49" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="C49" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="H49" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="24" t="s">
+      <c r="D49" s="24" t="s">
         <v>156</v>
       </c>
+      <c r="E49" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I49" s="25" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1" spans="1:9">
-      <c r="A50" s="25"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E50" s="26"/>
-      <c r="F50" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>159</v>
+      <c r="A50" s="26"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="27"/>
+      <c r="F50" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" s="25" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="51" ht="47" customHeight="1" spans="1:9">
-      <c r="A51" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="F51" s="24" t="s">
+      <c r="A51" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G51" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="H51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="C51" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="24" t="s">
         <v>165</v>
       </c>
+      <c r="E51" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="52" ht="47" customHeight="1" spans="1:9">
-      <c r="A52" s="25"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="G52" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="H52" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I52" s="24" t="s">
+      <c r="A52" s="26"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24" t="s">
         <v>169</v>
       </c>
+      <c r="E52" s="26"/>
+      <c r="F52" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="53" ht="52" customHeight="1" spans="1:9">
-      <c r="A53" s="25"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="G53" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="24" t="s">
+      <c r="A53" s="26"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24" t="s">
         <v>173</v>
       </c>
+      <c r="E53" s="26"/>
+      <c r="F53" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="54" ht="52" customHeight="1" spans="1:9">
-      <c r="A54" s="25"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I54" s="24" t="s">
-        <v>175</v>
+      <c r="A54" s="26"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="55" ht="39" customHeight="1" spans="1:9">
-      <c r="A55" s="25"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I55" s="24" t="s">
+      <c r="A55" s="26"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24" t="s">
         <v>179</v>
       </c>
+      <c r="E55" s="26"/>
+      <c r="F55" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="G55" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="56" ht="34" customHeight="1" spans="1:9">
-      <c r="A56" s="25"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I56" s="24" t="s">
+      <c r="A56" s="26"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24" t="s">
         <v>183</v>
       </c>
+      <c r="E56" s="26"/>
+      <c r="F56" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="57" ht="41" customHeight="1" spans="1:9">
-      <c r="A57" s="25"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="G57" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I57" s="24" t="s">
-        <v>186</v>
+      <c r="A57" s="26"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="27"/>
+      <c r="F57" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="G57" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3906,66 +3932,66 @@
     </row>
     <row r="2" customFormat="1" ht="33" customHeight="1" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:4">
-      <c r="A4" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>193</v>
+      <c r="A4" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" ht="254" customHeight="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
@@ -3973,10 +3999,10 @@
     </row>
     <row r="10" ht="27" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -4008,103 +4034,103 @@
     </row>
     <row r="2" ht="61" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>205</v>
+        <v>190</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="3" ht="61" customHeight="1" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4" ht="61" customHeight="1" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="37" customHeight="1" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1" spans="1:2">
-      <c r="A6" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="16">
         <v>45809</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="84" customHeight="1" spans="1:2">
-      <c r="A7" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>214</v>
+    <row r="7" customFormat="1" ht="70.7" spans="1:2">
+      <c r="A7" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="94" customHeight="1" spans="1:2">
-      <c r="A9" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="127.3" spans="1:2">
+      <c r="A9" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
     </row>
     <row r="11" customFormat="1" spans="1:2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
     </row>
     <row r="12" customFormat="1" spans="1:2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4128,38 +4154,38 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" ht="54" customHeight="1" spans="1:2">
-      <c r="A2" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="14">
         <v>176</v>
       </c>
     </row>
     <row r="3" ht="54" customHeight="1" spans="1:2">
-      <c r="A3" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="14">
+      <c r="A3" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="54" customHeight="1" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B4" s="5">
         <v>1.5</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1" spans="1:2">
-      <c r="A5" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="15">
         <f>B3*B4</f>
         <v>0</v>
       </c>
@@ -4191,115 +4217,115 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="61" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>190</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="5" ht="72" customHeight="1" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4311,11 +4337,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="39.3693693693694" style="7" customWidth="1"/>
-    <col min="2" max="2" width="43.4234234234234" style="1" customWidth="1"/>
+    <col min="2" max="2" width="89.4684684684685" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="37" customHeight="1" spans="1:2">
@@ -4326,131 +4352,139 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:2">
+    <row r="2" ht="37" customHeight="1" spans="1:2">
       <c r="A2" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>235</v>
+        <v>190</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2">
-      <c r="A3" s="9" t="s">
-        <v>236</v>
+      <c r="A3" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:2">
-      <c r="A4" s="9" t="s">
-        <v>237</v>
+      <c r="A4" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2">
-      <c r="A5" s="9" t="s">
-        <v>239</v>
+      <c r="A5" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2">
-      <c r="A6" s="9" t="s">
-        <v>241</v>
+      <c r="A6" s="11" t="s">
+        <v>243</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2">
-      <c r="A7" s="9" t="s">
-        <v>243</v>
+      <c r="A7" s="11" t="s">
+        <v>245</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2">
-      <c r="A8" s="9" t="s">
-        <v>245</v>
+      <c r="A8" s="11" t="s">
+        <v>247</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2">
-      <c r="A9" s="9" t="s">
-        <v>247</v>
+      <c r="A9" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:2">
-      <c r="A10" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="5">
         <v>13950406998</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2">
-      <c r="A11" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="3">
+    <row r="12" ht="24" customHeight="1" spans="1:2">
+      <c r="A12" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="3">
         <f>'5、预估工作量-元数据录入'!B3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:2">
-      <c r="A12" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12" s="3"/>
-    </row>
     <row r="13" ht="24" customHeight="1" spans="1:2">
-      <c r="A13" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>253</v>
-      </c>
+      <c r="A13" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2">
-      <c r="A14" s="9" t="s">
-        <v>254</v>
+      <c r="A14" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2">
-      <c r="A15" s="9" t="s">
-        <v>255</v>
+      <c r="A15" s="11" t="s">
+        <v>258</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2">
-      <c r="A16" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:2">
+      <c r="A17" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="3">
         <f>'5、预估工作量-元数据录入'!B3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:2">
-      <c r="A17" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="B17" s="3"/>
+    <row r="18" ht="24" customHeight="1" spans="1:2">
+      <c r="A18" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4471,42 +4505,42 @@
   <sheetData>
     <row r="1" ht="47" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="6"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
@@ -1044,7 +1044,7 @@
     <t>IF(L{row}=\"新增\",1,IF(L{row}=\"复用\",1/3,0))</t>
   </si>
   <si>
-    <t>附件3-${工单编号}-${工单名称}（${子系统（模块）}）项目需求清单V1.0.0.docx</t>
+    <t>附件3-${工单编号}-${工单名称}（${子系统（模块）}）项目需求清单V1.0.0.xlsx</t>
   </si>
   <si>
     <t>项目信息概览-标题</t>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="7"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
@@ -903,7 +903,7 @@
     <t>【客户端类型】一级模块-二级模块-三级模块-功能过程</t>
   </si>
   <si>
-    <t>计算依据归类判定原则</t>
+    <t>计算依据归类判定原则列表</t>
   </si>
   <si>
     <t>EI:1)修改或增加界面的个数
@@ -1358,12 +1358,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="3"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
@@ -298,7 +298,10 @@
   </si>
   <si>
     <t>如果该单元格中有#AI生成#的标记，表示对应的内容由AI去生成
-如果该单元格中没有#AI生成#的标记，表示采用该单元格的原文</t>
+如果该单元格中没有#AI生成#的标记，表示采用该单元格的原文
+如果要优化AI生成的结果，让AI生成更合适的内容，可修改用户提示词和系统提示词
+用户提示词：该单元格的内容，除了“#AI生成#”标记外，其他都将作为用户提示词
+系统提示词：可在配置文件（ai_system_prompts_config.yaml）中修改</t>
   </si>
   <si>
     <t>项目</t>
@@ -339,25 +342,53 @@
     <t>总体描述</t>
   </si>
   <si>
-    <t>#AI生成#根据${工单内容}，生成总体描述，要求200~300字</t>
+    <t>#AI生成#
+请根据以下工单内容，生成“总体描述”。
+${工单内容}
+要求：
+- 首句概括业务目标和定位
+- 从“解决什么问题、服务谁、带来什么价值”角度展开
+- 不出现编号，语言商务正式，有感染力
+- 200-350字</t>
   </si>
   <si>
     <t>建设目标</t>
   </si>
   <si>
-    <t>#AI生成#根据${工单内容}，生成建设目标，要求200~300字</t>
+    <t>#AI生成#
+请根据以下工单内容，生成“建设目标”。
+${工单内容}
+要求：
+- 首句点明核心目的
+- 从“要做出什么能力、达到什么效果”角度写
+- 不出现编号，用连贯分句衔接
+- 150-250字</t>
   </si>
   <si>
     <t>建设必要性</t>
   </si>
   <si>
-    <t>#AI生成#根据${工单内容}，生成建设必要性，要求200~300字</t>
+    <t>#AI生成#
+请根据以下工单内容，生成“建设必要性”。
+${工单内容}
+要求：
+- 从现状问题或业务痛点出发
+- 说明为什么必须建、不建会怎样
+- 语气有说服力、紧迫感，但不夸张
+- 180-280字</t>
   </si>
   <si>
     <t>系统概况</t>
   </si>
   <si>
-    <t>#AI生成#根据${工单内容}，生成系统概况，要求200~300字</t>
+    <t>#AI生成#
+请根据以下工单内容，生成“系统概况”。
+${工单内容}
+要求：
+- 开头一句话概括系统是什么、服务什么目标
+- 然后按工单内容提供的模块信息，用精简方式列出核心功能
+- 此章节可以保留编号结构（如1、2、3或（1）（2）（3）），便于快速概览
+- 总字数150-250字</t>
   </si>
   <si>
     <t>入口</t>
@@ -972,7 +1003,7 @@
     <t>#AI生成#
 根据${三级模块}的全部内容，概括项目的主要功能模块，判定系统属于业务处理还是管理支撑类型。
 按照以下示例的格式输出：
-本项目主要完成功能参与垂直行业配置、行业人员认证、下单页面自定义配置、用户下单、订单查看等模块，属于业务处理。</t>
+本项目主要完成功能xxx、xxx、...等模块，属于xxx。</t>
   </si>
   <si>
     <t>调整因子中的子系统名称</t>
@@ -985,14 +1016,9 @@
   </si>
   <si>
     <t>#AI生成#
-根据${三级模块整体功能描述}中的全部内容，提取其中涉及与可靠性方面的模块，生成一段可靠性需求描述，
-要求包含：
-1. 结合项目业务场景说明可靠性为何重要；
-2. 数据备份和容灾要求；
-3. 7×24小时不间断运行要求；
-4. 模块更新不相互影响的要求
-请参考以下示例风格：
-结合业务场景说明可靠性重要性，提出具体的数据备份和容灾措施，明确运行时间和模块独立性要求。</t>
+根据功能清单，提取其中涉及与可靠性方面的模块，生成一句关于可靠性业务描述。
+功能清单：
+${三级模块整体功能描述}</t>
   </si>
   <si>
     <t>数量</t>
@@ -1998,8 +2024,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2569,7 +2595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1" spans="1:2">
+    <row r="6" ht="114" customHeight="1" spans="1:2">
       <c r="A6" s="36" t="s">
         <v>4</v>
       </c>
@@ -2687,7 +2713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="183.45" spans="1:2">
+    <row r="4" ht="228" customHeight="1" spans="1:2">
       <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
@@ -2695,7 +2721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="24" customHeight="1" spans="1:2">
+    <row r="5" customFormat="1" ht="141" spans="1:2">
       <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
@@ -2703,7 +2729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:2">
+    <row r="6" customFormat="1" ht="141" spans="1:2">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
@@ -2711,7 +2737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:2">
+    <row r="7" customFormat="1" ht="141" spans="1:2">
       <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
@@ -2719,7 +2745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:2">
+    <row r="8" customFormat="1" ht="141" spans="1:2">
       <c r="A8" s="17" t="s">
         <v>20</v>
       </c>
@@ -4072,7 +4098,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="70.7" spans="1:2">
+    <row r="7" customFormat="1" ht="83" customHeight="1" spans="1:2">
       <c r="A7" s="17" t="s">
         <v>216</v>
       </c>
@@ -4088,7 +4114,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="127.3" spans="1:2">
+    <row r="9" customFormat="1" ht="157" customHeight="1" spans="1:2">
       <c r="A9" s="17" t="s">
         <v>220</v>
       </c>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -1001,9 +1001,9 @@
   </si>
   <si>
     <t>#AI生成#
-根据${三级模块}的全部内容，概括项目的主要功能模块，判定系统属于业务处理还是管理支撑类型。
+根据${三级模块}的全部内容，概括项目的主要功能模块。
 按照以下示例的格式输出：
-本项目主要完成功能xxx、xxx、...等模块，属于xxx。</t>
+本项目主要完成功能xxx、xxx、...等模块，属于业务处理。</t>
   </si>
   <si>
     <t>调整因子中的子系统名称</t>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="6"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
@@ -304,6 +304,10 @@
 系统提示词：可在配置文件（ai_system_prompts_config.yaml）中修改</t>
   </si>
   <si>
+    <t>关于项目需求说明书.docx的目录更新
+手动跟新：找到目录，更新域-&gt;更新整个目录</t>
+  </si>
+  <si>
     <t>项目</t>
   </si>
   <si>
@@ -917,9 +921,6 @@
   </si>
   <si>
     <t>和乐业</t>
-  </si>
-  <si>
-    <t>3、闽市移需【202501】17658 号-关于构建垂直行业场景化营销的需求（和乐业）-FPA工作量评估</t>
   </si>
   <si>
     <t>资产标识</t>
@@ -1628,7 +1629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1679,6 +1680,50 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1812,7 +1857,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1824,34 +1869,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1936,7 +1981,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2050,6 +2095,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2581,8 +2638,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:B6"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A4:B11"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.2162162162162" customWidth="1"/>
     <col min="2" max="2" width="93.8198198198198" customWidth="1"/>
@@ -2612,7 +2669,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10" ht="27" customHeight="1" spans="1:2">
+      <c r="A10" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="39"/>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:2">
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:B11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2630,7 +2700,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>222</v>
@@ -2700,66 +2770,66 @@
   <sheetData>
     <row r="1" s="30" customFormat="1" ht="38" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:2">
       <c r="A2" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:2">
       <c r="A3" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="228" customHeight="1" spans="1:2">
       <c r="A4" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="141" spans="1:2">
       <c r="A5" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="141" spans="1:2">
       <c r="A6" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="141" spans="1:2">
       <c r="A7" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="141" spans="1:2">
       <c r="A8" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2788,60 +2858,60 @@
   <sheetData>
     <row r="1" s="20" customFormat="1" ht="49" customHeight="1" spans="1:9">
       <c r="A1" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9">
       <c r="A2" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="28.3" spans="1:9">
@@ -2852,13 +2922,13 @@
       <c r="E3" s="26"/>
       <c r="F3" s="24"/>
       <c r="G3" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:9">
@@ -2869,13 +2939,13 @@
       <c r="E4" s="26"/>
       <c r="F4" s="24"/>
       <c r="G4" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:9">
@@ -2886,13 +2956,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="24"/>
       <c r="G5" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="28.3" spans="1:9">
@@ -2903,13 +2973,13 @@
       <c r="E6" s="26"/>
       <c r="F6" s="24"/>
       <c r="G6" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="39" customHeight="1" spans="1:9">
@@ -2920,13 +2990,13 @@
       <c r="E7" s="26"/>
       <c r="F7" s="24"/>
       <c r="G7" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="14.15" spans="1:9">
@@ -2937,13 +3007,13 @@
       <c r="E8" s="27"/>
       <c r="F8" s="24"/>
       <c r="G8" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" ht="47" customHeight="1" spans="1:9">
@@ -2951,22 +3021,22 @@
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
       <c r="D9" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:9">
@@ -2977,13 +3047,13 @@
       <c r="E10" s="26"/>
       <c r="F10" s="24"/>
       <c r="G10" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
@@ -2994,13 +3064,13 @@
       <c r="E11" s="26"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="14.15" spans="1:9">
@@ -3011,38 +3081,38 @@
       <c r="E12" s="27"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="28.3" spans="1:9">
       <c r="A13" s="26"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" ht="99" spans="1:9">
@@ -3053,13 +3123,13 @@
       <c r="E14" s="26"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="99" spans="1:9">
@@ -3070,13 +3140,13 @@
       <c r="E15" s="26"/>
       <c r="F15" s="24"/>
       <c r="G15" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="14.15" spans="1:9">
@@ -3087,13 +3157,13 @@
       <c r="E16" s="26"/>
       <c r="F16" s="24"/>
       <c r="G16" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="28.3" spans="1:9">
@@ -3104,13 +3174,13 @@
       <c r="E17" s="26"/>
       <c r="F17" s="24"/>
       <c r="G17" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="14.15" spans="1:9">
@@ -3121,13 +3191,13 @@
       <c r="E18" s="27"/>
       <c r="F18" s="24"/>
       <c r="G18" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="28.3" spans="1:9">
@@ -3135,22 +3205,22 @@
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
       <c r="D19" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="99" spans="1:9">
@@ -3161,13 +3231,13 @@
       <c r="E20" s="26"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="99" spans="1:9">
@@ -3178,13 +3248,13 @@
       <c r="E21" s="26"/>
       <c r="F21" s="24"/>
       <c r="G21" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="14.15" spans="1:9">
@@ -3195,13 +3265,13 @@
       <c r="E22" s="26"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="28.3" spans="1:9">
@@ -3212,13 +3282,13 @@
       <c r="E23" s="26"/>
       <c r="F23" s="24"/>
       <c r="G23" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="14.15" spans="1:9">
@@ -3229,38 +3299,38 @@
       <c r="E24" s="27"/>
       <c r="F24" s="24"/>
       <c r="G24" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="42.45" spans="1:9">
       <c r="A25" s="26"/>
       <c r="B25" s="24"/>
       <c r="C25" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="42.45" spans="1:9">
@@ -3271,13 +3341,13 @@
       <c r="E26" s="26"/>
       <c r="F26" s="24"/>
       <c r="G26" s="25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" ht="42.45" spans="1:9">
@@ -3288,13 +3358,13 @@
       <c r="E27" s="27"/>
       <c r="F27" s="24"/>
       <c r="G27" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" ht="56.55" spans="1:9">
@@ -3302,22 +3372,22 @@
       <c r="B28" s="24"/>
       <c r="C28" s="26"/>
       <c r="D28" s="24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="56.55" spans="1:9">
@@ -3328,13 +3398,13 @@
       <c r="E29" s="26"/>
       <c r="F29" s="24"/>
       <c r="G29" s="25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" ht="28.3" spans="1:9">
@@ -3345,38 +3415,38 @@
       <c r="E30" s="27"/>
       <c r="F30" s="24"/>
       <c r="G30" s="25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" ht="28.3" spans="1:9">
       <c r="A31" s="26"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" ht="28.3" spans="1:9">
@@ -3387,13 +3457,13 @@
       <c r="E32" s="26"/>
       <c r="F32" s="24"/>
       <c r="G32" s="25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I32" s="25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" ht="28.3" spans="1:9">
@@ -3404,13 +3474,13 @@
       <c r="E33" s="26"/>
       <c r="F33" s="24"/>
       <c r="G33" s="25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" ht="14.15" spans="1:9">
@@ -3421,13 +3491,13 @@
       <c r="E34" s="26"/>
       <c r="F34" s="24"/>
       <c r="G34" s="25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I34" s="25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" ht="14.15" spans="1:9">
@@ -3438,13 +3508,13 @@
       <c r="E35" s="26"/>
       <c r="F35" s="24"/>
       <c r="G35" s="25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" ht="14.15" spans="1:9">
@@ -3455,38 +3525,38 @@
       <c r="E36" s="27"/>
       <c r="F36" s="24"/>
       <c r="G36" s="25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1" spans="1:9">
       <c r="A37" s="26"/>
       <c r="B37" s="24"/>
       <c r="C37" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:9">
@@ -3497,13 +3567,13 @@
       <c r="E38" s="26"/>
       <c r="F38" s="24"/>
       <c r="G38" s="25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I38" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:9">
@@ -3514,13 +3584,13 @@
       <c r="E39" s="26"/>
       <c r="F39" s="24"/>
       <c r="G39" s="25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" spans="1:9">
@@ -3531,13 +3601,13 @@
       <c r="E40" s="26"/>
       <c r="F40" s="24"/>
       <c r="G40" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:9">
@@ -3548,13 +3618,13 @@
       <c r="E41" s="26"/>
       <c r="F41" s="24"/>
       <c r="G41" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" spans="1:9">
@@ -3565,13 +3635,13 @@
       <c r="E42" s="26"/>
       <c r="F42" s="24"/>
       <c r="G42" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" spans="1:9">
@@ -3579,20 +3649,20 @@
       <c r="B43" s="24"/>
       <c r="C43" s="24"/>
       <c r="D43" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:9">
@@ -3603,38 +3673,38 @@
       <c r="E44" s="27"/>
       <c r="F44" s="24"/>
       <c r="G44" s="25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I44" s="25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1" spans="1:9">
       <c r="A45" s="26"/>
       <c r="B45" s="24"/>
       <c r="C45" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:9">
@@ -3645,13 +3715,13 @@
       <c r="E46" s="26"/>
       <c r="F46" s="24"/>
       <c r="G46" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1" spans="1:9">
@@ -3659,20 +3729,20 @@
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E47" s="26"/>
       <c r="F47" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I47" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:9">
@@ -3683,40 +3753,40 @@
       <c r="E48" s="27"/>
       <c r="F48" s="24"/>
       <c r="G48" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I48" s="25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:9">
       <c r="A49" s="26"/>
       <c r="B49" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="D49" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>154</v>
-      </c>
       <c r="F49" s="25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I49" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1" spans="1:9">
@@ -3724,49 +3794,49 @@
       <c r="B50" s="24"/>
       <c r="C50" s="29"/>
       <c r="D50" s="24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I50" s="25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" ht="47" customHeight="1" spans="1:9">
       <c r="A51" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="23" t="s">
-        <v>164</v>
-      </c>
       <c r="F51" s="25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" ht="47" customHeight="1" spans="1:9">
@@ -3774,20 +3844,20 @@
       <c r="B52" s="24"/>
       <c r="C52" s="24"/>
       <c r="D52" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E52" s="26"/>
       <c r="F52" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" ht="52" customHeight="1" spans="1:9">
@@ -3795,20 +3865,20 @@
       <c r="B53" s="24"/>
       <c r="C53" s="24"/>
       <c r="D53" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E53" s="26"/>
       <c r="F53" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" ht="52" customHeight="1" spans="1:9">
@@ -3819,13 +3889,13 @@
       <c r="E54" s="26"/>
       <c r="F54" s="24"/>
       <c r="G54" s="25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I54" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" ht="39" customHeight="1" spans="1:9">
@@ -3833,20 +3903,20 @@
       <c r="B55" s="24"/>
       <c r="C55" s="24"/>
       <c r="D55" s="24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E55" s="26"/>
       <c r="F55" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1" spans="1:9">
@@ -3854,20 +3924,20 @@
       <c r="B56" s="24"/>
       <c r="C56" s="24"/>
       <c r="D56" s="24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E56" s="26"/>
       <c r="F56" s="25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" ht="41" customHeight="1" spans="1:9">
@@ -3875,20 +3945,20 @@
       <c r="B57" s="24"/>
       <c r="C57" s="24"/>
       <c r="D57" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E57" s="27"/>
       <c r="F57" s="25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3950,41 +4020,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="3"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="30.981981981982" style="1" customWidth="1"/>
     <col min="2" max="2" width="106.297297297297" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="42" customHeight="1" spans="1:4">
+    <row r="1" s="2" customFormat="1" ht="42" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" ht="33" customHeight="1" spans="1:4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="33" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" ht="33" customHeight="1" spans="1:4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" ht="33" customHeight="1" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1" spans="1:4">
+    <row r="4" ht="45" customHeight="1" spans="1:2">
       <c r="A4" s="15" t="s">
         <v>195</v>
       </c>
@@ -3992,7 +4059,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" spans="1:4">
+    <row r="5" ht="45" customHeight="1" spans="1:2">
       <c r="A5" s="5" t="s">
         <v>197</v>
       </c>
@@ -4000,7 +4067,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" ht="254" customHeight="1" spans="1:4">
+    <row r="6" ht="254" customHeight="1" spans="1:2">
       <c r="A6" s="5" t="s">
         <v>199</v>
       </c>
@@ -4008,7 +4075,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1" spans="1:4">
+    <row r="7" ht="56" customHeight="1" spans="1:2">
       <c r="A7" s="5" t="s">
         <v>201</v>
       </c>
@@ -4016,7 +4083,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:4">
+    <row r="8" ht="36" customHeight="1" spans="1:2">
       <c r="A8" s="5" t="s">
         <v>203</v>
       </c>
@@ -4024,7 +4091,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:4">
+    <row r="9" ht="36" customHeight="1" spans="1:2">
       <c r="A9" s="5" t="s">
         <v>205</v>
       </c>
@@ -4032,7 +4099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="27" customHeight="1" spans="1:4">
+    <row r="10" ht="27" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>206</v>
       </c>
@@ -4061,15 +4128,15 @@
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="61" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>208</v>
@@ -4186,7 +4253,7 @@
   <sheetData>
     <row r="1" ht="43" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>222</v>
@@ -4235,8 +4302,8 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="7" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="24.4774774774775" style="1" customWidth="1"/>
     <col min="2" max="2" width="122.774774774775" style="1" customWidth="1"/>
@@ -4244,15 +4311,15 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="31" customHeight="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="61" customHeight="1" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>227</v>
@@ -4305,66 +4372,6 @@
       <c r="B8" s="14" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:2">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:2">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:2">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:2">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:2">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4385,15 +4392,15 @@
   <sheetData>
     <row r="1" ht="37" customHeight="1" spans="1:2">
       <c r="A1" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:2">
       <c r="A2" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>239</v>

--- a/data/功能清单-录入-模板.xlsx
+++ b/data/功能清单-录入-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="798" activeTab="2"/>
+    <workbookView windowWidth="18351" windowHeight="8211" tabRatio="798" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="模板说明" sheetId="6" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
   </si>
   <si>
     <t>#AI生成#
-根据${三级模块}的全部内容，概括项目的主要功能模块。
+根据${三级模块}的全部内容，概括项目的主要功能模块。不少于50字。
 按照以下示例的格式输出：
 本项目主要完成功能xxx、xxx、...等模块，属于业务处理。</t>
   </si>
@@ -1017,7 +1017,7 @@
   </si>
   <si>
     <t>#AI生成#
-根据功能清单，提取其中涉及与可靠性方面的模块，生成一句关于可靠性业务描述。
+根据功能清单，提取其中涉及与可靠性方面的模块，生成一句关于可靠性业务描述。不少于50字。
 功能清单：
 ${三级模块整体功能描述}</t>
   </si>
